--- a/20_项目/02_光与朽项目/01_策划文档/光与朽_第二三章_怪物美术资产清单.xlsx
+++ b/20_项目/02_光与朽项目/01_策划文档/光与朽_第二三章_怪物美术资产清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27431" windowHeight="13068" activeTab="1"/>
+    <workbookView windowWidth="22488" windowHeight="11231" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="第二章-熔岩虚空" sheetId="1" r:id="rId1"/>
@@ -63,6 +63,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>中大椭圆形，边缘起伏冒泡。比</t>
     </r>
     <r>
@@ -122,6 +128,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>三对惊恐小眼，挤在一起。呆萌但比</t>
     </r>
     <r>
@@ -145,6 +157,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>身体表面覆盖</t>
     </r>
     <r>
@@ -171,6 +189,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>像过载细胞一样包裹着多个核心的流体。打死后分裂出</t>
     </r>
     <r>
@@ -198,6 +222,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>极度膨胀的正圆形，但前端收尖呈水滴</t>
     </r>
     <r>
@@ -960,7 +990,81 @@
     <t>Sprite+Shader</t>
   </si>
   <si>
-    <t>Boss裂缝发光层(Order 19)：橙红色裂缝光随Boss受伤逐渐扩大(Shader参数驱动)</t>
+    <r>
+      <t>Boss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>裂缝发光层</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(Order 19)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：橙红色裂缝光随</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Boss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>受伤逐渐扩大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(Shader</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参数驱动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1A1A2E"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <t>岩浆光芒</t>
@@ -1111,7 +1215,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1186,13 +1290,6 @@
       <color rgb="FF1A1A2E"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1339,7 +1436,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="45">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1354,31 +1451,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F2FD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBDEFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90CAF9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3E0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F2FD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBDEFB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90CAF9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F5F5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1705,152 +1826,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1870,6 +1991,24 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1877,22 +2016,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1905,19 +2044,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2276,17 +2421,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:6">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="14" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="25" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2311,87 +2456,87 @@
       </c>
     </row>
     <row r="6" ht="50.4" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="27" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="50.4" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" ht="50.4" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" ht="37.2" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="28" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="25" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2416,47 +2561,47 @@
       </c>
     </row>
     <row r="13" ht="38.4" spans="1:6">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="30" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" ht="38.4" spans="1:6">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="30" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="25" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2481,27 +2626,27 @@
       </c>
     </row>
     <row r="18" ht="62.4" spans="1:6">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="D18" s="24" t="s">
+      <c r="D18" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="32" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="25" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2526,142 +2671,142 @@
       </c>
     </row>
     <row r="23" ht="26.4" spans="1:6">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" ht="26.4" spans="1:6">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="23" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="25" ht="26.4" spans="1:6">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="21" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="26" ht="26.4" spans="1:6">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="23" t="s">
         <v>80</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="23" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="27" ht="26.4" spans="1:6">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="28" ht="26.4" spans="1:6">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="23" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="29" ht="39.6" spans="1:6">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="21" t="s">
         <v>100</v>
       </c>
     </row>
@@ -2692,17 +2837,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.4" spans="1:6">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="14" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2727,87 +2872,87 @@
       </c>
     </row>
     <row r="6" ht="39.6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="10" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="7" ht="49.2" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="10" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="8" ht="50.4" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="10" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="9" ht="37.2" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="10" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="15" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2832,47 +2977,47 @@
       </c>
     </row>
     <row r="13" ht="50.4" spans="1:6">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="17" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="14" ht="49.2" spans="1:6">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="17" t="s">
         <v>137</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="17" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="15" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2897,27 +3042,27 @@
       </c>
     </row>
     <row r="18" ht="75.6" spans="1:6">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="19" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="15" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2942,142 +3087,142 @@
       </c>
     </row>
     <row r="23" ht="26.4" spans="1:6">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="21" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="24" ht="39.6" spans="1:6">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="22" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="23" t="s">
         <v>152</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="C24" s="23" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="D24" s="23" t="s">
         <v>154</v>
       </c>
-      <c r="E24" s="17" t="s">
+      <c r="E24" s="23" t="s">
         <v>155</v>
       </c>
-      <c r="F24" s="17" t="s">
+      <c r="F24" s="23" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="25" ht="39.6" spans="1:6">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="21" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="26" ht="39.6" spans="1:6">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="22" t="s">
         <v>163</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="17" t="s">
+      <c r="C26" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="F26" s="17" t="s">
+      <c r="F26" s="23" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="27" ht="26.4" spans="1:6">
-      <c r="A27" s="14" t="s">
+      <c r="A27" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="B27" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="21" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="28" ht="39.6" spans="1:6">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="B28" s="17" t="s">
+      <c r="B28" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="E28" s="17" t="s">
+      <c r="E28" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="F28" s="17" t="s">
+      <c r="F28" s="23" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="29" ht="52.8" spans="1:6">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B29" s="15" t="s">
+      <c r="B29" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="21" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3148,19 +3293,19 @@
       </c>
     </row>
     <row r="5" ht="26.4" spans="1:5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="6" t="s">
         <v>201</v>
       </c>
     </row>
@@ -3233,87 +3378,87 @@
       </c>
     </row>
     <row r="10" ht="26.4" spans="1:5">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="6" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="11" ht="25.2" spans="1:5">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="8" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="12" ht="26.4" spans="1:5">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="6" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="14" ht="24" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="10" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="15" ht="25.2" spans="1:5">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>235</v>
       </c>
     </row>
@@ -3352,19 +3497,19 @@
       </c>
     </row>
     <row r="18" ht="26.4" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="12" t="s">
         <v>245</v>
       </c>
     </row>
@@ -3386,36 +3531,36 @@
       </c>
     </row>
     <row r="20" ht="26.4" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="4" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="21" ht="26.4" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="4" t="s">
         <v>256</v>
       </c>
     </row>
@@ -3454,53 +3599,53 @@
       </c>
     </row>
     <row r="24" ht="25.2" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="4" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="25" ht="25.2" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="4" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="26" ht="26.4" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="4" t="s">
         <v>272</v>
       </c>
     </row>
